--- a/output/pdf_financials_xlsx/Z.H.xlsx
+++ b/output/pdf_financials_xlsx/Z.H.xlsx
@@ -6165,22 +6165,22 @@
         <v>5.575553</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>5.575553</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>5.575553</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>5.575553</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>5.575553</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>5.575553</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>5.575553</v>
       </c>
     </row>
     <row r="93">
@@ -7688,13 +7688,13 @@
         <v>2.31552</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0.308278</v>
+        <v>-2.259043</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>23.642767</v>
+        <v>19.105432</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>5.979695</v>
+        <v>5.038143</v>
       </c>
       <c r="N118" s="3" t="n">
         <v>0</v>
@@ -9924,7 +9924,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -10854,7 +10858,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -11780,7 +11788,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -12312,7 +12324,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -16200,7 +16216,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -20874,7 +20894,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
@@ -32290,7 +32314,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/Z.H.xlsx
+++ b/output/pdf_financials_xlsx/Z.H.xlsx
@@ -1059,25 +1059,25 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.003918</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000163</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.02307</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.06929200000000001</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.024307</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.004676</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.000365</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -2048,25 +2048,25 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.035083</v>
+        <v>-0.039001</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.572036</v>
+        <v>-0.572199</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-5.025856</v>
+        <v>-5.048926</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-8.702396999999999</v>
+        <v>-8.771689</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-3.862456</v>
+        <v>-3.886763</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-2.226288</v>
+        <v>-2.230964</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.943235</v>
+        <v>-0.9436</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-0.368964</v>
@@ -2170,25 +2170,25 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.035083</v>
+        <v>-0.039001</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.572036</v>
+        <v>-0.572199</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-5.010945</v>
+        <v>-5.034015</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-8.652958</v>
+        <v>-8.722250000000001</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-3.800889</v>
+        <v>-3.825196</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.182329</v>
+        <v>-2.187005</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.914473</v>
+        <v>-0.914838</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-0.368865</v>
@@ -2514,37 +2514,37 @@
         <v>0.052415</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.007506</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.663663</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.5253640000000001</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.01342</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.013166</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.004076</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.00098</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.007464</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.010812</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.006331</v>
       </c>
     </row>
     <row r="35">
@@ -2636,37 +2636,37 @@
         <v>0.052415</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.007506</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.663663</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.546</v>
+        <v>1.071364</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.139243</v>
+        <v>0.152663</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.013166</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.004076</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.045</v>
+        <v>0.04598</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.02</v>
+        <v>0.027464</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0.035</v>
+        <v>0.045812</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0.068</v>
+        <v>0.07433099999999999</v>
       </c>
     </row>
     <row r="37">
@@ -3368,28 +3368,28 @@
         <v>0.024897</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.021397</v>
+        <v>0.013891</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.849351</v>
+        <v>0.185688</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.901129</v>
+        <v>0.375765</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.08344699999999999</v>
+        <v>0.07002700000000001</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>0.035118</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.020896</v>
+        <v>0.00773</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.010555</v>
+        <v>0.006479</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.00098</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="3" t="n">
         <v>0</v>
@@ -8948,7 +8948,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -20684,7 +20684,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -60724,7 +60724,7 @@
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E497" t="inlineStr">
@@ -62910,7 +62910,7 @@
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E518" s="5" t="n">

--- a/output/pdf_financials_xlsx/Z.H.xlsx
+++ b/output/pdf_financials_xlsx/Z.H.xlsx
@@ -760,25 +760,25 @@
         <v>0.129112</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.403744</v>
+        <v>0.409077</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.510537</v>
+        <v>0.542537</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.519968</v>
+        <v>0.551968</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.399504</v>
+        <v>0.431504</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.259765</v>
+        <v>0.291765</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.268788</v>
+        <v>0.284788</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.314392</v>
+        <v>0.318392</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0.801324</v>
@@ -943,19 +943,19 @@
         <v>0.129112</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.403744</v>
+        <v>0.409077</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.510537</v>
+        <v>0.542537</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.519968</v>
+        <v>0.551968</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.399504</v>
+        <v>0.431504</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.259765</v>
+        <v>0.291765</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>0.400701</v>
@@ -1652,10 +1652,10 @@
         <v>-26.441644</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>-7.685402</v>
+        <v>-1.09955</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>-7.685402</v>
+        <v>-0.520887</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>-0.42776</v>
@@ -7240,13 +7240,13 @@
         <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.099407</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.160603</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.005739</v>
       </c>
       <c r="G111" s="3" t="n">
         <v>0</v>
@@ -7261,7 +7261,7 @@
         <v>0</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-0.047899</v>
       </c>
       <c r="L111" s="3" t="n">
         <v>0</v>
@@ -7444,7 +7444,7 @@
         <v>0</v>
       </c>
       <c r="K114" s="3" t="n">
-        <v>0</v>
+        <v>-0.433305</v>
       </c>
       <c r="L114" s="3" t="n">
         <v>0</v>
@@ -7508,10 +7508,10 @@
         <v>0</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>0.48547</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>0.164262</v>
       </c>
       <c r="N115" s="3" t="n">
         <v>0</v>
@@ -7529,7 +7529,7 @@
         <v>0</v>
       </c>
       <c r="S115" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="116">
@@ -8687,13 +8687,13 @@
         <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.099407</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.160603</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.005739</v>
       </c>
       <c r="G134" s="3" t="n">
         <v>0</v>
@@ -8708,7 +8708,7 @@
         <v>0</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-0.047899</v>
       </c>
       <c r="L134" s="3" t="n">
         <v>0</v>
@@ -8750,13 +8750,13 @@
         <v>-0.240853</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-3.130753</v>
+        <v>-3.23016</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-8.402633</v>
+        <v>-8.563236</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-3.982995</v>
+        <v>-3.988734</v>
       </c>
       <c r="G135" s="3" t="n">
         <v>-2.12172</v>
@@ -8771,7 +8771,7 @@
         <v>-0.834797</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>-4.488695</v>
+        <v>-4.536594</v>
       </c>
       <c r="L135" s="3" t="n">
         <v>-0.19969</v>
@@ -26848,7 +26848,11 @@
           <t>Proceeds of sale of marketable securities</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>-</t>
@@ -30554,7 +30558,11 @@
           <t>Common shares issued for cash</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr">
         <is>
           <t>-</t>
@@ -32104,7 +32112,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E224" t="inlineStr">
         <is>
           <t>-</t>
@@ -33364,7 +33376,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr">
         <is>
           <t>-</t>
@@ -33470,7 +33486,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr"/>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr">
         <is>
           <t>-</t>
@@ -36694,7 +36714,11 @@
           <t>Common shares issued for cash 4</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E268" t="inlineStr">
         <is>
           <t>-</t>
@@ -39108,7 +39132,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E291" t="inlineStr">
         <is>
           <t>-</t>
@@ -39210,7 +39238,11 @@
           <t>Common shares issued for cash</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr"/>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E292" t="inlineStr">
         <is>
           <t>-</t>
@@ -49582,7 +49614,11 @@
           <t>LOSS FROM CONTINUING OPERATIONS</t>
         </is>
       </c>
-      <c r="D391" t="inlineStr"/>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E391" t="inlineStr">
         <is>
           <t>-</t>
@@ -57180,7 +57216,11 @@
           <t>Directors’ fees 14</t>
         </is>
       </c>
-      <c r="D463" t="inlineStr"/>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E463" t="inlineStr">
         <is>
           <t>-</t>
@@ -58336,7 +58376,11 @@
           <t>Directors’ fees 10</t>
         </is>
       </c>
-      <c r="D474" t="inlineStr"/>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E474" t="inlineStr">
         <is>
           <t>-</t>
@@ -59720,7 +59764,11 @@
           <t>Directors' fees 3</t>
         </is>
       </c>
-      <c r="D487" t="inlineStr"/>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E487" t="inlineStr">
         <is>
           <t>-</t>
@@ -62590,7 +62638,11 @@
           <t>Directors’ fees</t>
         </is>
       </c>
-      <c r="D515" t="inlineStr"/>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E515" t="inlineStr">
         <is>
           <t>-</t>
